--- a/sampleprojects/CorporateTax/excel/states/MT_corp.xlsx
+++ b/sampleprojects/CorporateTax/excel/states/MT_corp.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="111">
   <si>
     <t>DT: Determine MT Filing Requirement</t>
   </si>
@@ -70,7 +70,7 @@
     <t>Meets economic nexus threshold ($100K gross receipts or 200 transactions); result.mt_gross_receipts is greater than or equal to result.mt_economic_nexus_threshold</t>
   </si>
   <si>
-    <t>result.mt_gross_receipts &gt;= result.mt_economic_nexus_threshold</t>
+    <t>mt_result.gross_receipts &gt;= mt_result.economic_nexus_threshold</t>
   </si>
   <si>
     <t>-</t>
@@ -85,7 +85,7 @@
     <t>Physical nexus - filing required</t>
   </si>
   <si>
-    <t>set result.mt_has_nexus = true;</t>
+    <t>set mt_result.has_nexus = true;</t>
   </si>
   <si>
     <t>X</t>
@@ -97,7 +97,7 @@
     <t>No nexus - no filing required</t>
   </si>
   <si>
-    <t>set result.mt_has_nexus = false; set result.mt_tax_liability = 0.0;</t>
+    <t>set mt_result.has_nexus = false; set mt_result.tax_liability = 0.0;</t>
   </si>
   <si>
     <t>DT: Calculate MT Income Adjustments</t>
@@ -115,19 +115,19 @@
     <t>Has Montana nexus</t>
   </si>
   <si>
-    <t>result.mt_has_nexus is equal to true</t>
+    <t>mt_result.has_nexus is equal to true</t>
   </si>
   <si>
     <t>Calculate Montana state additions and subtractions; Calculate state-specific income adjustments</t>
   </si>
   <si>
-    <t>set result.mt_state_additions = 0.0; if result.mt_us_interest_income != 0.0 then set result.mt_state_additions = result.mt_state_additions + result.mt_us_interest_income; endif set result.mt_state_subtractions = 0.0; if result.mt_municipal_interest != 0.0 then set result.mt_state_subtractions = result.mt_state_subtractions + result.mt_municipal_interest; endif add (("Montana additions: $" + string value of (result.mt_state_additions)) + ", subtractions: $") + string value of (result.mt_state_subtractions) to job.audit_trail;</t>
+    <t>set mt_result.state_additions = 0.0; if mt_result.us_interest_income != 0.0 then set mt_result.state_additions = mt_result.state_additions + mt_result.us_interest_income; endif set mt_result.state_subtractions = 0.0; if mt_result.municipal_interest != 0.0 then set mt_result.state_subtractions = mt_result.state_subtractions + mt_result.municipal_interest; endif add (("Montana additions: $" + string value of (mt_result.state_additions)) + ", subtractions: $") + string value of (mt_result.state_subtractions) to job.audit_trail;</t>
   </si>
   <si>
     <t>No nexus - no adjustments</t>
   </si>
   <si>
-    <t>set result.mt_state_additions = 0.0; set result.mt_state_subtractions = 0.0;</t>
+    <t>set mt_result.state_additions = 0.0; set mt_result.state_subtractions = 0.0;</t>
   </si>
   <si>
     <t>DT: Calculate MT State Tax</t>
@@ -145,31 +145,31 @@
     <t>Has positive taxable income; result.mt_apportioned_income is greater than 0</t>
   </si>
   <si>
-    <t>result.mt_apportioned_income &gt; 0.0</t>
+    <t>mt_result.apportioned_income &gt; 0.0</t>
   </si>
   <si>
     <t>Made water's edge election</t>
   </si>
   <si>
-    <t>result.mt_waters_edge_election is equal to true</t>
+    <t>mt_result.waters_edge_election is equal to true</t>
   </si>
   <si>
     <t>Calculate Montana corporate tax (standard rate 6.75%); Apply Montana 6.75% flat rate</t>
   </si>
   <si>
-    <t>set result.mt_taxable_income = the maximum of (result.mt_apportioned_income + result.mt_state_additions - result.mt_state_subtractions) and (0.0); set result.mt_tax_liability = the maximum of (result.mt_taxable_income * result.mt_corp_tax_rate - result.mt_state_credits) and (0.0); set result.mt_refund_or_owed = result.mt_estimated_payments - result.mt_tax_liability; add "Montana taxable income: $" + string value of (result.mt_taxable_income) to job.audit_trail; add "Montana tax liability (6.75% standard rate): $" + string value of (result.mt_tax_liability) to job.audit_trail;</t>
+    <t>set mt_result.taxable_income = the maximum of (mt_result.apportioned_income + mt_result.state_additions - mt_result.state_subtractions) and (0.0); set mt_result.tax_liability = the maximum of (mt_result.taxable_income * mt_result.corp_tax_rate - mt_result.state_credits) and (0.0); set mt_result.refund_or_owed = mt_result.estimated_payments - mt_result.tax_liability; add "Montana taxable income: $" + string value of (mt_result.taxable_income) to job.audit_trail; add "Montana tax liability (6.75% standard rate): $" + string value of (mt_result.tax_liability) to job.audit_trail;</t>
   </si>
   <si>
     <t>Calculate Montana corporate tax (water's edge rate 7.0%); Apply Montana 7.0% water's edge rate</t>
   </si>
   <si>
-    <t>set result.mt_taxable_income = the maximum of (result.mt_apportioned_income + result.mt_state_additions - result.mt_state_subtractions) and (0.0); set result.mt_tax_liability = the maximum of (result.mt_taxable_income * result.mt_corp_tax_rate_waters_edge - result.mt_state_credits) and (0.0); set result.mt_refund_or_owed = result.mt_estimated_payments - result.mt_tax_liability; add "Montana taxable income: $" + string value of (result.mt_taxable_income) to job.audit_trail; add "Montana tax liability (7.0% water's edge rate): $" + string value of (result.mt_tax_liability) to job.audit_trail;</t>
+    <t>set mt_result.taxable_income = the maximum of (mt_result.apportioned_income + mt_result.state_additions - mt_result.state_subtractions) and (0.0); set mt_result.tax_liability = the maximum of (mt_result.taxable_income * mt_result.corp_tax_rate_waters_edge - mt_result.state_credits) and (0.0); set mt_result.refund_or_owed = mt_result.estimated_payments - mt_result.tax_liability; add "Montana taxable income: $" + string value of (mt_result.taxable_income) to job.audit_trail; add "Montana tax liability (7.0% water's edge rate): $" + string value of (mt_result.tax_liability) to job.audit_trail;</t>
   </si>
   <si>
     <t>No taxable income - no tax liability</t>
   </si>
   <si>
-    <t>set result.mt_taxable_income = 0.0; set result.mt_tax_liability = 0.0;</t>
+    <t>set mt_result.taxable_income = 0.0; set mt_result.tax_liability = 0.0;</t>
   </si>
   <si>
     <t>No nexus - no tax liability</t>
@@ -217,10 +217,10 @@
     <t>Reference</t>
   </si>
   <si>
-    <t>apportionment</t>
-  </si>
-  <si>
-    <t>(8 attributes)</t>
+    <t>mt_apportionment</t>
+  </si>
+  <si>
+    <t>(4 attributes)</t>
   </si>
   <si>
     <t>apportionment_formula</t>
@@ -250,133 +250,103 @@
     <t>MT economic nexus gross receipts threshold: $100,000</t>
   </si>
   <si>
+    <t>state_tax_rate</t>
+  </si>
+  <si>
+    <t>0.0675</t>
+  </si>
+  <si>
+    <t>MT corporate income tax rate: 6.75% (7.0% for waters edge election)</t>
+  </si>
+  <si>
+    <t>transaction_threshold</t>
+  </si>
+  <si>
+    <t>integer</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>MT economic nexus transaction count threshold: 200 transactions</t>
+  </si>
+  <si>
+    <t>mt_result</t>
+  </si>
+  <si>
+    <t>(17 attributes)</t>
+  </si>
+  <si>
+    <t>apportioned_income</t>
+  </si>
+  <si>
+    <t>0.0</t>
+  </si>
+  <si>
+    <t>Declared from decision-table usage; referenced by MT but never declared (campaign #948 Phase 1)</t>
+  </si>
+  <si>
+    <t>corp_tax_rate</t>
+  </si>
+  <si>
+    <t>Form CIT instructions: a tax of 6.75 percent on total Montana net income</t>
+  </si>
+  <si>
+    <t>corp_tax_rate_waters_edge</t>
+  </si>
+  <si>
+    <t>0.07</t>
+  </si>
+  <si>
+    <t>Form CIT instructions: a valid water-s-edge election pays 7 percent</t>
+  </si>
+  <si>
+    <t>effective_rate</t>
+  </si>
+  <si>
+    <t>MT effective tax rate (6.75% standard, 7.0% with waters edge election)</t>
+  </si>
+  <si>
+    <t>estimated_payments</t>
+  </si>
+  <si>
+    <t>gross_receipts</t>
+  </si>
+  <si>
+    <t>has_nexus</t>
+  </si>
+  <si>
+    <t>boolean</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>municipal_interest</t>
+  </si>
+  <si>
+    <t>refund_or_owed</t>
+  </si>
+  <si>
     <t>state_additions</t>
   </si>
   <si>
-    <t>0.0</t>
-  </si>
-  <si>
-    <t>MT additions: federal interest income, state tax refunds, certain expenses, etc.</t>
-  </si>
-  <si>
-    <t>state_code</t>
-  </si>
-  <si>
-    <t>MT</t>
-  </si>
-  <si>
-    <t>Montana state code</t>
-  </si>
-  <si>
     <t>state_credits</t>
   </si>
   <si>
-    <t>MT tax credits: jobs creation, research, energy production, infrastructure, etc.</t>
-  </si>
-  <si>
     <t>state_subtractions</t>
   </si>
   <si>
-    <t>MT subtractions: MT municipal bond interest, state income taxes, MT NOL, etc.</t>
-  </si>
-  <si>
-    <t>state_tax_rate</t>
-  </si>
-  <si>
-    <t>0.0675</t>
-  </si>
-  <si>
-    <t>MT corporate income tax rate: 6.75% (7.0% for waters edge election)</t>
-  </si>
-  <si>
-    <t>transaction_threshold</t>
-  </si>
-  <si>
-    <t>integer</t>
-  </si>
-  <si>
-    <t>200</t>
-  </si>
-  <si>
-    <t>MT economic nexus transaction count threshold: 200 transactions</t>
-  </si>
-  <si>
-    <t>result</t>
-  </si>
-  <si>
-    <t>(17 attributes)</t>
-  </si>
-  <si>
-    <t>mt_apportioned_income</t>
-  </si>
-  <si>
-    <t>Declared from decision-table usage; referenced by MT but never declared (campaign #948 Phase 1)</t>
-  </si>
-  <si>
-    <t>mt_corp_tax_rate</t>
-  </si>
-  <si>
-    <t>Form CIT instructions: a tax of 6.75 percent on total Montana net income</t>
-  </si>
-  <si>
-    <t>mt_corp_tax_rate_waters_edge</t>
-  </si>
-  <si>
-    <t>0.07</t>
-  </si>
-  <si>
-    <t>Form CIT instructions: a valid water-s-edge election pays 7 percent</t>
-  </si>
-  <si>
-    <t>mt_economic_nexus_threshold</t>
-  </si>
-  <si>
-    <t>mt_effective_rate</t>
-  </si>
-  <si>
-    <t>MT effective tax rate (6.75% standard, 7.0% with waters edge election)</t>
-  </si>
-  <si>
-    <t>mt_estimated_payments</t>
-  </si>
-  <si>
-    <t>mt_gross_receipts</t>
-  </si>
-  <si>
-    <t>mt_has_nexus</t>
-  </si>
-  <si>
-    <t>boolean</t>
-  </si>
-  <si>
-    <t>false</t>
-  </si>
-  <si>
-    <t>mt_municipal_interest</t>
-  </si>
-  <si>
-    <t>mt_refund_or_owed</t>
-  </si>
-  <si>
-    <t>mt_state_additions</t>
-  </si>
-  <si>
-    <t>mt_state_credits</t>
-  </si>
-  <si>
-    <t>mt_state_subtractions</t>
-  </si>
-  <si>
-    <t>mt_tax_liability</t>
-  </si>
-  <si>
-    <t>mt_taxable_income</t>
-  </si>
-  <si>
-    <t>mt_us_interest_income</t>
-  </si>
-  <si>
-    <t>mt_waters_edge_election</t>
+    <t>tax_liability</t>
+  </si>
+  <si>
+    <t>taxable_income</t>
+  </si>
+  <si>
+    <t>us_interest_income</t>
+  </si>
+  <si>
+    <t>waters_edge_election</t>
   </si>
   <si>
     <t>MT waters edge election - if true, rate is 7.0% instead of 6.75%</t>
@@ -2849,14 +2819,14 @@
       <c r="B7" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>69</v>
+      <c r="C7" s="11" t="s">
+        <v>81</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>8</v>
@@ -2865,7 +2835,7 @@
         <v>71</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>8</v>
@@ -2884,194 +2854,194 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="H8" s="16" t="s">
+      <c r="A8" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="I8" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>8</v>
-      </c>
+      <c r="B8" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G9" s="8" t="s">
+      <c r="D9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>71</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="M9" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M9" s="7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="8" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G10" s="7" t="s">
+      <c r="D10" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="8" t="s">
         <v>71</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M10" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M10" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>8</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="F11" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G11" s="8" t="s">
+      <c r="F11" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G11" s="7" t="s">
         <v>71</v>
       </c>
       <c r="H11" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="I11" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="M11" s="8" t="s">
+      <c r="I11" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M11" s="7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
+      <c r="A12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H12" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="8" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="s">
         <v>8</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>74</v>
@@ -3089,7 +3059,7 @@
         <v>71</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I13" s="7" t="s">
         <v>8</v>
@@ -3112,7 +3082,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>74</v>
@@ -3121,7 +3091,7 @@
         <v>8</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>8</v>
@@ -3130,7 +3100,7 @@
         <v>71</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="I14" s="8" t="s">
         <v>8</v>
@@ -3153,7 +3123,7 @@
         <v>8</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>74</v>
@@ -3162,7 +3132,7 @@
         <v>8</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>8</v>
@@ -3171,7 +3141,7 @@
         <v>71</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="I15" s="7" t="s">
         <v>8</v>
@@ -3194,16 +3164,16 @@
         <v>8</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>74</v>
+        <v>98</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>99</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>8</v>
@@ -3212,7 +3182,7 @@
         <v>71</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="I16" s="8" t="s">
         <v>8</v>
@@ -3235,7 +3205,7 @@
         <v>8</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C17" s="11" t="s">
         <v>74</v>
@@ -3244,7 +3214,7 @@
         <v>8</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>8</v>
@@ -3253,7 +3223,7 @@
         <v>71</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="I17" s="7" t="s">
         <v>8</v>
@@ -3276,7 +3246,7 @@
         <v>8</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C18" s="11" t="s">
         <v>74</v>
@@ -3285,7 +3255,7 @@
         <v>8</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>8</v>
@@ -3294,7 +3264,7 @@
         <v>71</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="I18" s="8" t="s">
         <v>8</v>
@@ -3317,7 +3287,7 @@
         <v>8</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>74</v>
@@ -3326,7 +3296,7 @@
         <v>8</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>8</v>
@@ -3335,7 +3305,7 @@
         <v>71</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="I19" s="7" t="s">
         <v>8</v>
@@ -3358,16 +3328,16 @@
         <v>8</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>109</v>
+        <v>104</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>74</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>8</v>
@@ -3376,7 +3346,7 @@
         <v>71</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="I20" s="8" t="s">
         <v>8</v>
@@ -3399,7 +3369,7 @@
         <v>8</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C21" s="11" t="s">
         <v>74</v>
@@ -3408,7 +3378,7 @@
         <v>8</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>8</v>
@@ -3417,7 +3387,7 @@
         <v>71</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="I21" s="7" t="s">
         <v>8</v>
@@ -3440,7 +3410,7 @@
         <v>8</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C22" s="11" t="s">
         <v>74</v>
@@ -3449,7 +3419,7 @@
         <v>8</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>8</v>
@@ -3458,7 +3428,7 @@
         <v>71</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="I22" s="8" t="s">
         <v>8</v>
@@ -3481,7 +3451,7 @@
         <v>8</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C23" s="11" t="s">
         <v>74</v>
@@ -3490,7 +3460,7 @@
         <v>8</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>8</v>
@@ -3499,7 +3469,7 @@
         <v>71</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="I23" s="7" t="s">
         <v>8</v>
@@ -3522,7 +3492,7 @@
         <v>8</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C24" s="11" t="s">
         <v>74</v>
@@ -3531,7 +3501,7 @@
         <v>8</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>8</v>
@@ -3540,7 +3510,7 @@
         <v>71</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="I24" s="8" t="s">
         <v>8</v>
@@ -3563,16 +3533,16 @@
         <v>8</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>74</v>
+        <v>109</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>99</v>
       </c>
       <c r="D25" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="F25" s="7" t="s">
         <v>8</v>
@@ -3581,7 +3551,7 @@
         <v>71</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="I25" s="7" t="s">
         <v>8</v>
@@ -3596,170 +3566,6 @@
         <v>8</v>
       </c>
       <c r="M25" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G26" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="H26" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="I26" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J26" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="K26" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="L26" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="M26" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="H27" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="I27" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J27" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="K27" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="L27" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M27" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B28" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G28" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="H28" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="I28" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J28" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="K28" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="L28" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="M28" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="H29" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="I29" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J29" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="K29" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="L29" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M29" s="7" t="s">
         <v>8</v>
       </c>
     </row>
